--- a/improvement/manufacturing/plan-03.xlsx
+++ b/improvement/manufacturing/plan-03.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>28名（うち製造現場20名・検査3名）</t>
+          <t>18名（うち製造現場12名・検査2名）</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>750万円（従業員5人以下・一般型。規模により最大8,000万円）</t>
+          <t>一般型。従業員規模により変動し、小規模な事業者で750万円程度〜最大8,000万円</t>
         </is>
       </c>
     </row>
